--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ESTUDIANTES LUGO RIO DE GALICIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ESTUDIANTES LUGO RIO DE GALICIA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>44.833</v>
+        <v>47.2166</v>
       </c>
       <c r="E2" t="n">
-        <v>38.6335</v>
+        <v>40.8118</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1998</v>
+        <v>6.4047</v>
       </c>
       <c r="G2" t="n">
         <v>19.0377</v>
@@ -610,13 +610,13 @@
         <v>62.0839</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4361999999999995</v>
+        <v>2.8197</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.547499999999999</v>
+        <v>-3.3692</v>
       </c>
       <c r="U2" t="n">
-        <v>5.984</v>
+        <v>6.189</v>
       </c>
       <c r="V2" t="n">
         <v>16.3502</v>
@@ -643,13 +643,13 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>23.8779</v>
+        <v>11.5924</v>
       </c>
       <c r="E3" t="n">
-        <v>22.8837</v>
+        <v>12.6829</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9945000000000002</v>
+        <v>-1.0905</v>
       </c>
       <c r="G3" t="n">
         <v>3.6256</v>
@@ -688,13 +688,13 @@
         <v>19.7805</v>
       </c>
       <c r="S3" t="n">
-        <v>17.4756</v>
+        <v>5.1899</v>
       </c>
       <c r="T3" t="n">
-        <v>11.8568</v>
+        <v>1.6562</v>
       </c>
       <c r="U3" t="n">
-        <v>5.6189</v>
+        <v>3.5337</v>
       </c>
       <c r="V3" t="n">
         <v>-2.1193</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>13.6574</v>
+        <v>6.199800000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2721</v>
+        <v>-0.5342000000000002</v>
       </c>
       <c r="F4" t="n">
-        <v>10.3855</v>
+        <v>6.734500000000001</v>
       </c>
       <c r="G4" t="n">
         <v>8.613200000000001</v>
@@ -766,13 +766,13 @@
         <v>29.9644</v>
       </c>
       <c r="S4" t="n">
-        <v>13.6649</v>
+        <v>6.2078</v>
       </c>
       <c r="T4" t="n">
-        <v>5.4043</v>
+        <v>1.5978</v>
       </c>
       <c r="U4" t="n">
-        <v>8.260999999999999</v>
+        <v>4.61</v>
       </c>
       <c r="V4" t="n">
         <v>-11.363</v>
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3155</v>
+        <v>-0.1329</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.07790000000000002</v>
+        <v>0.002399999999999958</v>
       </c>
       <c r="G5" t="n">
         <v>0.1415</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.457</v>
+        <v>-0.2745</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2194</v>
+        <v>-0.1392</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6523</v>
+        <v>-1.4697</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9584</v>
+        <v>-1.8561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3063</v>
+        <v>0.3865</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4094</v>
@@ -922,13 +922,13 @@
         <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.38</v>
+        <v>-0.1976</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.083</v>
+        <v>-0.002699999999999994</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.806800000000002</v>
+        <v>-3.3857</v>
       </c>
       <c r="E7" t="n">
-        <v>13.6632</v>
+        <v>-5.425000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-17.4699</v>
+        <v>2.0394</v>
       </c>
       <c r="G7" t="n">
-        <v>-12.0115</v>
+        <v>-10.2963</v>
       </c>
       <c r="H7" t="n">
-        <v>13.0945</v>
+        <v>-3.3106</v>
       </c>
       <c r="I7" t="n">
-        <v>-25.1061</v>
+        <v>-6.9855</v>
       </c>
       <c r="J7" t="n">
-        <v>29.4706</v>
+        <v>-1.9243</v>
       </c>
       <c r="K7" t="n">
-        <v>33.4025</v>
+        <v>2.6449</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.932199999999999</v>
+        <v>-4.5694</v>
       </c>
       <c r="M7" t="n">
-        <v>-41.4821</v>
+        <v>-8.3719</v>
       </c>
       <c r="N7" t="n">
-        <v>-20.3079</v>
+        <v>-5.956</v>
       </c>
       <c r="O7" t="n">
-        <v>-21.1736</v>
+        <v>-2.416</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.1334</v>
+        <v>8.812899999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-47.591</v>
+        <v>-7.0504</v>
       </c>
       <c r="R7" t="n">
-        <v>44.4574</v>
+        <v>15.8633</v>
       </c>
       <c r="S7" t="n">
-        <v>12.1322</v>
+        <v>-1.6018</v>
       </c>
       <c r="T7" t="n">
-        <v>6.3182</v>
+        <v>-0.3176</v>
       </c>
       <c r="U7" t="n">
-        <v>5.814299999999999</v>
+        <v>-1.2841</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7939999999999995</v>
+        <v>-0.3010000000000002</v>
       </c>
       <c r="W7" t="n">
-        <v>25.466</v>
+        <v>3.867599999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-26.2602</v>
+        <v>-4.1686</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.9183</v>
+        <v>-6.2691</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.524299999999999</v>
+        <v>-5.733199999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6062</v>
+        <v>-0.5359999999999983</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.2963</v>
+        <v>4.0133</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.3106</v>
+        <v>2.1324</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.9855</v>
+        <v>1.881</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9243</v>
+        <v>19.974</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6449</v>
+        <v>11.0298</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.5694</v>
+        <v>8.9442</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.3719</v>
+        <v>-15.9606</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.956</v>
+        <v>-8.8972</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.416</v>
+        <v>-7.0635</v>
       </c>
       <c r="P8" t="n">
-        <v>8.812899999999999</v>
+        <v>7.0501</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.0504</v>
+        <v>-24.6765</v>
       </c>
       <c r="R8" t="n">
-        <v>15.8633</v>
+        <v>31.727</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.1344</v>
+        <v>1.8579</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4168</v>
+        <v>0.7498999999999998</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.7178</v>
+        <v>1.1079</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3010000000000002</v>
+        <v>-19.1908</v>
       </c>
       <c r="W8" t="n">
-        <v>3.867599999999999</v>
+        <v>-1.7799</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.1686</v>
+        <v>-17.411</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.1808</v>
+        <v>-11.9323</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6041</v>
+        <v>7.5953</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.577</v>
+        <v>-19.5274</v>
       </c>
       <c r="G9" t="n">
-        <v>4.0133</v>
+        <v>-12.0115</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1324</v>
+        <v>13.0945</v>
       </c>
       <c r="I9" t="n">
-        <v>1.881</v>
+        <v>-25.1061</v>
       </c>
       <c r="J9" t="n">
-        <v>19.974</v>
+        <v>29.4706</v>
       </c>
       <c r="K9" t="n">
-        <v>11.0298</v>
+        <v>33.4025</v>
       </c>
       <c r="L9" t="n">
-        <v>8.9442</v>
+        <v>-3.932199999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.9606</v>
+        <v>-41.4821</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.8972</v>
+        <v>-20.3079</v>
       </c>
       <c r="O9" t="n">
-        <v>-7.0635</v>
+        <v>-21.1736</v>
       </c>
       <c r="P9" t="n">
-        <v>7.0501</v>
+        <v>-3.1334</v>
       </c>
       <c r="Q9" t="n">
-        <v>-24.6765</v>
+        <v>-47.591</v>
       </c>
       <c r="R9" t="n">
-        <v>31.727</v>
+        <v>44.4574</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9462</v>
+        <v>4.0069</v>
       </c>
       <c r="T9" t="n">
-        <v>1.879</v>
+        <v>0.2504000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06709999999999994</v>
+        <v>3.756600000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-19.1908</v>
+        <v>-0.7939999999999995</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.7799</v>
+        <v>25.466</v>
       </c>
       <c r="X9" t="n">
-        <v>-17.411</v>
+        <v>-26.2602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-20.6464</v>
+        <v>-14.3986</v>
       </c>
       <c r="E10" t="n">
-        <v>-13.9921</v>
+        <v>-5.691399999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.654000000000001</v>
+        <v>-8.707600000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-16.9334</v>
+        <v>-36.3525</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3924999999999992</v>
+        <v>-23.7152</v>
       </c>
       <c r="I10" t="n">
-        <v>-17.3262</v>
+        <v>-12.6372</v>
       </c>
       <c r="J10" t="n">
-        <v>21.7327</v>
+        <v>11.8023</v>
       </c>
       <c r="K10" t="n">
-        <v>22.991</v>
+        <v>4.3245</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2578</v>
+        <v>7.477600000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-38.6667</v>
+        <v>-48.1546</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.5985</v>
+        <v>-28.0397</v>
       </c>
       <c r="O10" t="n">
-        <v>-16.0683</v>
+        <v>-20.1147</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.1336</v>
+        <v>5.092199999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-58.7542</v>
+        <v>-51.7039</v>
       </c>
       <c r="R10" t="n">
-        <v>55.6208</v>
+        <v>56.7958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5949</v>
+        <v>-7.0692</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7456</v>
+        <v>-9.0687</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3406</v>
+        <v>1.9991</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01569999999999949</v>
+        <v>23.931</v>
       </c>
       <c r="W10" t="n">
-        <v>22.2842</v>
+        <v>43.2794</v>
       </c>
       <c r="X10" t="n">
-        <v>-22.2684</v>
+        <v>-19.3488</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>-21.227</v>
+        <v>-18.4481</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.708</v>
+        <v>-13.0543</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.5191</v>
+        <v>-5.3937</v>
       </c>
       <c r="G11" t="n">
         <v>-7.6348</v>
@@ -1312,13 +1312,13 @@
         <v>10.1839</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.6915</v>
+        <v>-4.9123</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.0156</v>
+        <v>-3.3618</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.6759</v>
+        <v>-1.5502</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3757</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-36.6408</v>
+        <v>-22.1652</v>
       </c>
       <c r="E12" t="n">
-        <v>-31.1284</v>
+        <v>-16.7585</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.5122</v>
+        <v>-5.406599999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>1.679100000000001</v>
+        <v>-16.9334</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0373</v>
+        <v>0.3924999999999992</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3581999999999992</v>
+        <v>-17.3262</v>
       </c>
       <c r="J12" t="n">
-        <v>19.1116</v>
+        <v>21.7327</v>
       </c>
       <c r="K12" t="n">
-        <v>12.6529</v>
+        <v>22.991</v>
       </c>
       <c r="L12" t="n">
-        <v>6.4581</v>
+        <v>-1.2578</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.4324</v>
+        <v>-38.6667</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.616</v>
+        <v>-22.5985</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.8164</v>
+        <v>-16.0683</v>
       </c>
       <c r="P12" t="n">
-        <v>-15.4719</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q12" t="n">
-        <v>-43.4781</v>
+        <v>-58.7542</v>
       </c>
       <c r="R12" t="n">
-        <v>28.0063</v>
+        <v>55.6208</v>
       </c>
       <c r="S12" t="n">
-        <v>-16.2101</v>
+        <v>-2.114199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-10.0784</v>
+        <v>-2.0211</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.1316</v>
+        <v>-0.09309999999999979</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.637799999999999</v>
+        <v>0.01569999999999949</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3169</v>
+        <v>22.2842</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.954699999999999</v>
+        <v>-22.2684</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-37.5755</v>
+        <v>-25.8739</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.382</v>
+        <v>-24.249</v>
       </c>
       <c r="F13" t="n">
-        <v>-23.1936</v>
+        <v>-1.6247</v>
       </c>
       <c r="G13" t="n">
-        <v>-24.1261</v>
+        <v>1.679100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.253299999999999</v>
+        <v>2.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>-14.8731</v>
+        <v>-0.3581999999999992</v>
       </c>
       <c r="J13" t="n">
-        <v>9.2981</v>
+        <v>19.1116</v>
       </c>
       <c r="K13" t="n">
-        <v>11.412</v>
+        <v>12.6529</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.114</v>
+        <v>6.4581</v>
       </c>
       <c r="M13" t="n">
-        <v>-33.4247</v>
+        <v>-17.4324</v>
       </c>
       <c r="N13" t="n">
-        <v>-20.6652</v>
+        <v>-10.616</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.7593</v>
+        <v>-6.8164</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0002999999999995784</v>
+        <v>-15.4719</v>
       </c>
       <c r="Q13" t="n">
-        <v>-32.9023</v>
+        <v>-43.4781</v>
       </c>
       <c r="R13" t="n">
-        <v>32.9021</v>
+        <v>28.0063</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.389799999999999</v>
+        <v>-5.4435</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.1188</v>
+        <v>-3.199</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2707</v>
+        <v>-2.2443</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.0594</v>
+        <v>-6.637799999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>16.3415</v>
+        <v>3.3169</v>
       </c>
       <c r="X13" t="n">
-        <v>-20.401</v>
+        <v>-9.954699999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-38.3649</v>
+        <v>-30.6486</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.9787</v>
+        <v>-11.4771</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.3862</v>
+        <v>-19.1714</v>
       </c>
       <c r="G14" t="n">
-        <v>-36.3525</v>
+        <v>-24.1261</v>
       </c>
       <c r="H14" t="n">
-        <v>-23.7152</v>
+        <v>-9.253299999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.6372</v>
+        <v>-14.8731</v>
       </c>
       <c r="J14" t="n">
-        <v>11.8023</v>
+        <v>9.2981</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3245</v>
+        <v>11.412</v>
       </c>
       <c r="L14" t="n">
-        <v>7.477600000000001</v>
+        <v>-2.114</v>
       </c>
       <c r="M14" t="n">
-        <v>-48.1546</v>
+        <v>-33.4247</v>
       </c>
       <c r="N14" t="n">
-        <v>-28.0397</v>
+        <v>-20.6652</v>
       </c>
       <c r="O14" t="n">
-        <v>-20.1147</v>
+        <v>-12.7593</v>
       </c>
       <c r="P14" t="n">
-        <v>5.092199999999999</v>
+        <v>-0.0002999999999995784</v>
       </c>
       <c r="Q14" t="n">
-        <v>-51.7039</v>
+        <v>-32.9023</v>
       </c>
       <c r="R14" t="n">
-        <v>56.7958</v>
+        <v>32.9021</v>
       </c>
       <c r="S14" t="n">
-        <v>-31.0352</v>
+        <v>-2.4628</v>
       </c>
       <c r="T14" t="n">
-        <v>-24.3563</v>
+        <v>-4.2143</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.6795</v>
+        <v>1.7509</v>
       </c>
       <c r="V14" t="n">
-        <v>23.931</v>
+        <v>-4.0594</v>
       </c>
       <c r="W14" t="n">
-        <v>43.2794</v>
+        <v>16.3415</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.3488</v>
+        <v>-20.401</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-88.96000000000001</v>
+        <v>-69.7153</v>
       </c>
       <c r="E15" t="n">
-        <v>-30.0611</v>
+        <v>-23.8241</v>
       </c>
       <c r="F15" t="n">
-        <v>-58.8976</v>
+        <v>-45.8904</v>
       </c>
       <c r="G15" t="n">
         <v>-70.6536</v>
@@ -1606,7 +1606,7 @@
         <v>48.0498</v>
       </c>
       <c r="M15" t="n">
-        <v>-300.8218</v>
+        <v>-300.8217999999999</v>
       </c>
       <c r="N15" t="n">
         <v>-171.9155</v>
@@ -1624,16 +1624,16 @@
         <v>387.7771</v>
       </c>
       <c r="S15" t="n">
-        <v>-23.23780000000001</v>
+        <v>-3.993700000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>-27.8641</v>
+        <v>-21.6274</v>
       </c>
       <c r="U15" t="n">
-        <v>4.626800000000002</v>
+        <v>17.6336</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.819499999999991</v>
+        <v>-6.8195</v>
       </c>
       <c r="W15" t="n">
         <v>143.6663</v>
